--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:18:58+00:00</t>
+    <t>2026-09-01T13:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:59:06+00:00</t>
+    <t>2026-09-03T08:45:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T08:45:38+00:00</t>
+    <t>2026-09-08T11:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:58:20+00:00</t>
+    <t>2026-09-08T12:58:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1399,7 +1399,7 @@
   &lt;coding&gt;
     &lt;system value="http://snomed.info/sct"/&gt;
     &lt;code value="726007"/&gt;
-    &lt;display value="Pathology consultation, comprehensive, records and specimen with report (procedure)"/&gt;
+    &lt;display value="Pathology consultation, comprehensive, records and specimen with report"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:58:28+00:00</t>
+    <t>2026-09-08T14:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-service-request.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:07:59+00:00</t>
+    <t>2026-09-08T14:30:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
